--- a/dataset_t6_grouped/results2/G5/G5_T8387_W0075F0003T0006Z000C1N72_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T8387_W0075F0003T0006Z000C1N72_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>9.437781237009064</v>
+        <v>1.533639451013973</v>
       </c>
       <c r="D2" t="n">
-        <v>9.535908743038354</v>
+        <v>1.549585170743732</v>
       </c>
       <c r="E2" t="n">
-        <v>9.149368332863173</v>
+        <v>1.486772354090266</v>
       </c>
       <c r="F2" t="n">
-        <v>9.150430482827669</v>
+        <v>1.486944953459496</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>32.89490488992562</v>
+        <v>5.345422044612913</v>
       </c>
       <c r="D3" t="n">
-        <v>32.79862901614828</v>
+        <v>5.329777215124096</v>
       </c>
       <c r="E3" t="n">
-        <v>9.149368332863173</v>
+        <v>1.486772354090266</v>
       </c>
       <c r="F3" t="n">
-        <v>9.150430482827669</v>
+        <v>1.486944953459496</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>33.55389369974645</v>
+        <v>5.452507726208799</v>
       </c>
       <c r="D4" t="n">
-        <v>33.41767843550178</v>
+        <v>5.430372745769039</v>
       </c>
       <c r="E4" t="n">
-        <v>9.149368332863173</v>
+        <v>1.486772354090266</v>
       </c>
       <c r="F4" t="n">
-        <v>9.150430482827669</v>
+        <v>1.486944953459496</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>32.78372232575357</v>
+        <v>5.327354877934955</v>
       </c>
       <c r="D5" t="n">
-        <v>32.81799960464421</v>
+        <v>5.332924935754684</v>
       </c>
       <c r="E5" t="n">
-        <v>9.149368332863173</v>
+        <v>1.486772354090266</v>
       </c>
       <c r="F5" t="n">
-        <v>9.150430482827669</v>
+        <v>1.486944953459496</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>8.941976964418261</v>
+        <v>1.453071256717968</v>
       </c>
       <c r="D6" t="n">
-        <v>8.853709289557395</v>
+        <v>1.438727759553077</v>
       </c>
       <c r="E6" t="n">
-        <v>9.149368332863173</v>
+        <v>1.486772354090266</v>
       </c>
       <c r="F6" t="n">
-        <v>9.150430482827669</v>
+        <v>1.486944953459496</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>12.52018569196787</v>
+        <v>2.034530174944779</v>
       </c>
       <c r="D7" t="n">
-        <v>12.54203192413427</v>
+        <v>2.038080187671819</v>
       </c>
       <c r="E7" t="n">
-        <v>9.149368332863173</v>
+        <v>1.486772354090266</v>
       </c>
       <c r="F7" t="n">
-        <v>9.150430482827669</v>
+        <v>1.486944953459496</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>28.85542891208878</v>
+        <v>4.689007198214426</v>
       </c>
       <c r="D8" t="n">
-        <v>28.74758307280698</v>
+        <v>4.671482249331135</v>
       </c>
       <c r="E8" t="n">
-        <v>9.149368332863173</v>
+        <v>1.486772354090266</v>
       </c>
       <c r="F8" t="n">
-        <v>9.150430482827669</v>
+        <v>1.486944953459496</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>8.383819861162387</v>
+        <v>1.362370727438888</v>
       </c>
       <c r="D9" t="n">
-        <v>8.282633216756647</v>
+        <v>1.345927897722955</v>
       </c>
       <c r="E9" t="n">
-        <v>9.149368332863173</v>
+        <v>1.486772354090266</v>
       </c>
       <c r="F9" t="n">
-        <v>9.150430482827669</v>
+        <v>1.486944953459496</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>25.88763861360725</v>
+        <v>4.206741274711178</v>
       </c>
       <c r="D10" t="n">
-        <v>25.9705895323653</v>
+        <v>4.220220799009362</v>
       </c>
       <c r="E10" t="n">
-        <v>9.149368332863173</v>
+        <v>1.486772354090266</v>
       </c>
       <c r="F10" t="n">
-        <v>9.150430482827669</v>
+        <v>1.486944953459496</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>16.90751830360864</v>
+        <v>2.747471724336405</v>
       </c>
       <c r="D11" t="n">
-        <v>16.86168317081856</v>
+        <v>2.740023515258016</v>
       </c>
       <c r="E11" t="n">
-        <v>9.149368332863173</v>
+        <v>1.486772354090266</v>
       </c>
       <c r="F11" t="n">
-        <v>9.150430482827669</v>
+        <v>1.486944953459496</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>19.6868460912657</v>
+        <v>3.199112489830676</v>
       </c>
       <c r="D12" t="n">
-        <v>19.77183551165096</v>
+        <v>3.21292327064328</v>
       </c>
       <c r="E12" t="n">
-        <v>9.149368332863173</v>
+        <v>1.486772354090266</v>
       </c>
       <c r="F12" t="n">
-        <v>9.150430482827669</v>
+        <v>1.486944953459496</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>24.05421534803348</v>
+        <v>3.908809994055441</v>
       </c>
       <c r="D13" t="n">
-        <v>24.19138148016643</v>
+        <v>3.931099490527046</v>
       </c>
       <c r="E13" t="n">
-        <v>9.149368332863173</v>
+        <v>1.486772354090266</v>
       </c>
       <c r="F13" t="n">
-        <v>9.150430482827669</v>
+        <v>1.486944953459496</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>27.94185615212665</v>
+        <v>4.540551624720582</v>
       </c>
       <c r="D14" t="n">
-        <v>28.00730063866279</v>
+        <v>4.551186353782703</v>
       </c>
       <c r="E14" t="n">
-        <v>9.149368332863173</v>
+        <v>1.486772354090266</v>
       </c>
       <c r="F14" t="n">
-        <v>9.150430482827669</v>
+        <v>1.486944953459496</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>30.2564377514841</v>
+        <v>4.916671134616166</v>
       </c>
       <c r="D15" t="n">
-        <v>30.37351897243757</v>
+        <v>4.935696833021106</v>
       </c>
       <c r="E15" t="n">
-        <v>9.149368332863173</v>
+        <v>1.486772354090266</v>
       </c>
       <c r="F15" t="n">
-        <v>9.150430482827669</v>
+        <v>1.486944953459496</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
